--- a/samples/hanbit/structured/products.xlsx
+++ b/samples/hanbit/structured/products.xlsx
@@ -425,7 +425,7 @@
     <col width="24.8" customWidth="1" min="2" max="2"/>
     <col width="13.6" customWidth="1" min="3" max="3"/>
     <col width="7.2" customWidth="1" min="4" max="4"/>
-    <col width="13.6" customWidth="1" min="5" max="5"/>
+    <col width="15.2" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>140600</v>
+        <v>6100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>271600</v>
+        <v>11800</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>244200</v>
+        <v>57900</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>420300</v>
+        <v>99500</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -599,11 +599,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>365800</v>
+        <v>10300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -629,11 +629,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>685600</v>
+        <v>19200</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -659,11 +659,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6600</v>
+        <v>24100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -689,11 +689,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9300</v>
+        <v>34300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,11 +719,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>92900</v>
+        <v>33700</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -749,11 +749,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>118500</v>
+        <v>43000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -779,11 +779,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11400</v>
+        <v>132500</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -809,11 +809,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21900</v>
+        <v>255700</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -839,11 +839,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8200</v>
+        <v>230300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13800</v>
+        <v>387200</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>38500</v>
+        <v>139500</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -929,11 +929,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>54100</v>
+        <v>195400</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>28500</v>
+        <v>139800</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>43600</v>
+        <v>214700</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1019,11 +1019,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223100</v>
+        <v>458900</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>385600</v>
+        <v>793100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>14400</v>
+        <v>13200</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>19300</v>
+        <v>17700</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>켤레</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>108600</v>
+        <v>80800</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1169,11 +1169,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>켤레</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>179600</v>
+        <v>133700</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>38400</v>
+        <v>10100</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>57200</v>
+        <v>14900</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1259,11 +1259,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>박스</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3500</v>
+        <v>16400</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>박스</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5100</v>
+        <v>23900</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>351000</v>
+        <v>168000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>496400</v>
+        <v>237700</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5500</v>
+        <v>15900</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8800</v>
+        <v>25800</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>147700</v>
+        <v>24700</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>280700</v>
+        <v>47100</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>159100</v>
+        <v>16800</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>304900</v>
+        <v>32300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>589700</v>
+        <v>118200</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>716400</v>
+        <v>143500</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6600</v>
+        <v>12900</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12100</v>
+        <v>23500</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1679,11 +1679,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>32800</v>
+        <v>4000</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>52600</v>
+        <v>6500</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5300</v>
+        <v>17000</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6600</v>
+        <v>21200</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1799,11 +1799,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>13000</v>
+        <v>5200</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1829,11 +1829,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>20400</v>
+        <v>8100</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1859,11 +1859,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>면</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6500</v>
+        <v>325500</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1889,11 +1889,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>면</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10700</v>
+        <v>536200</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3700</v>
+        <v>10800</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6400</v>
+        <v>18700</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1979,11 +1979,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>306700</v>
+        <v>9800</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2009,11 +2009,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>519200</v>
+        <v>16600</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>44000</v>
+        <v>125800</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>69800</v>
+        <v>200200</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>151200</v>
+        <v>146600</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>248600</v>
+        <v>241100</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2159,11 +2159,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>438500</v>
+        <v>2391500</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2189,11 +2189,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>752900</v>
+        <v>4106600</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>427100</v>
+        <v>18400</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>640000</v>
+        <v>27500</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>363900</v>
+        <v>47900</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>691400</v>
+        <v>91000</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2339,11 +2339,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>62600</v>
+        <v>33100</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2369,11 +2369,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>121600</v>
+        <v>64200</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>236200</v>
+        <v>29600</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>375400</v>
+        <v>47100</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2459,11 +2459,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>28700</v>
+        <v>668700</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>대</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>46900</v>
+        <v>1093800</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>243600</v>
+        <v>77600</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>516200</v>
+        <v>164400</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>31200</v>
+        <v>15700</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>44200</v>
+        <v>22300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2639,11 +2639,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>롤</t>
+          <t>묶음</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4200</v>
+        <v>16900</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2669,11 +2669,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>롤</t>
+          <t>묶음</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>7100</v>
+        <v>28200</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2699,11 +2699,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>롤</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7800</v>
+        <v>46100</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2729,11 +2729,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>롤</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>14300</v>
+        <v>85300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52700</v>
+        <v>36500</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>119600</v>
+        <v>82400</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>58200</v>
+        <v>28600</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106600</v>
+        <v>52800</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>138300</v>
+        <v>63800</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>283500</v>
+        <v>131000</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2939,11 +2939,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>롤</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>85100</v>
+        <v>112300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>롤</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>116300</v>
+        <v>153700</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2999,11 +2999,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>169400</v>
+        <v>172700</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3029,11 +3029,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>299500</v>
+        <v>305500</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3059,11 +3059,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>117000</v>
+        <v>205800</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3089,11 +3089,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>208600</v>
+        <v>367100</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3119,11 +3119,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>켤레</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>9600</v>
+        <v>7200</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3149,11 +3149,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>켤레</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>13100</v>
+        <v>9800</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28400</v>
+        <v>51400</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>35000</v>
+        <v>63300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>31200</v>
+        <v>110400</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>54000</v>
+        <v>190900</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3299,11 +3299,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>통</t>
+          <t>드럼</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>579100</v>
+        <v>734000</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3329,11 +3329,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>통</t>
+          <t>드럼</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>976500</v>
+        <v>1237700</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3359,11 +3359,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>통</t>
+          <t>박스</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>612700</v>
+        <v>94800</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3389,11 +3389,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>통</t>
+          <t>박스</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>915200</v>
+        <v>141600</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>110800</v>
+        <v>136500</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>160700</v>
+        <v>198000</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>166600</v>
+        <v>168100</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>251600</v>
+        <v>253700</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>28300</v>
+        <v>142500</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>47100</v>
+        <v>237800</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>21700</v>
+        <v>161100</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>40200</v>
+        <v>298900</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>266300</v>
+        <v>171500</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>361900</v>
+        <v>233100</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>96200</v>
+        <v>60300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>143700</v>
+        <v>90100</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>81500</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>140100</v>
+        <v>79600</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>13300</v>
+        <v>60400</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>29900</v>
+        <v>135800</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3899,11 +3899,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>통</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6800</v>
+        <v>19900</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>통</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>11500</v>
+        <v>33900</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3959,11 +3959,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>110000</v>
+        <v>104500</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>241800</v>
+        <v>229600</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>묶음</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6900</v>
+        <v>13500</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4049,11 +4049,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>묶음</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>13600</v>
+        <v>26700</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
